--- a/Sample_run/1/student/AnhDThe187386/OverallSummary.xlsx
+++ b/Sample_run/1/student/AnhDThe187386/OverallSummary.xlsx
@@ -61,7 +61,7 @@
     <x:t>TC6</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 9 FAIL (ALL-OR-NOTHING), 13 PASS</x:t>
+    <x:t>The operation was canceled.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -434,7 +434,7 @@
     <x:col min="2" max="2" width="7.282054" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="45.424911" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="44.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" s="1" customFormat="1">
